--- a/Сценарий 3.xlsx
+++ b/Сценарий 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\Desktop\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F7E49E2-7183-4A32-97E9-9376D0D3BF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45B0572-73C0-4DDC-81F6-68D4F356BF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3230,19 +3230,19 @@
         <v>71</v>
       </c>
       <c r="AM8" s="36">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="36">
-        <v>158.19999999999999</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="36">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="36">
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AQ8" s="36">
-        <v>205</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8061,11 +8061,11 @@
     <row r="74" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L74" s="27">
         <f>L84*0.973</f>
-        <v>126.49</v>
-      </c>
-      <c r="M74" s="79">
+        <v>0</v>
+      </c>
+      <c r="M74" s="79" t="e">
         <f>L74/$L$74</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N74" s="29">
         <v>0</v>
@@ -8076,11 +8076,11 @@
       </c>
       <c r="Q74" s="27">
         <f>Q84*0.973</f>
-        <v>153.92859999999999</v>
-      </c>
-      <c r="R74" s="79">
+        <v>0</v>
+      </c>
+      <c r="R74" s="79" t="e">
         <f>Q74/$Q$74</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S74" s="29">
         <v>0</v>
@@ -8091,11 +8091,11 @@
       </c>
       <c r="V74" s="27">
         <f>V84*0.973</f>
-        <v>194.6</v>
-      </c>
-      <c r="W74" s="79">
+        <v>0</v>
+      </c>
+      <c r="W74" s="79" t="e">
         <f>V74/$V$74</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X74" s="29">
         <v>0</v>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AA74" s="27">
         <f>AA84*0.973</f>
-        <v>197.90819999999999</v>
+        <v>39.348119999999994</v>
       </c>
       <c r="AB74" s="79">
         <f>AA74/$AA$74</f>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AF74" s="27">
         <f>AA84</f>
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AG74" s="28">
         <f t="shared" ref="AG74:AG84" si="80">AF74/$AF$74</f>
@@ -8138,11 +8138,11 @@
     <row r="75" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L75" s="31">
         <f t="shared" ref="L75:L83" si="82">L74+(L$84-L$74)/10</f>
-        <v>126.84099999999999</v>
-      </c>
-      <c r="M75" s="79">
+        <v>0</v>
+      </c>
+      <c r="M75" s="79" t="e">
         <f t="shared" ref="M75:M84" si="83">L75/$L$74</f>
-        <v>1.0027749229188079</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N75" s="33">
         <v>0.1</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="Q75" s="31">
         <f t="shared" ref="Q75:Q83" si="84">Q74+(Q$84-Q$74)/10</f>
-        <v>154.35574</v>
-      </c>
-      <c r="R75" s="79">
+        <v>0</v>
+      </c>
+      <c r="R75" s="79" t="e">
         <f t="shared" ref="R75:R84" si="85">Q75/$Q$74</f>
-        <v>1.0027749229188079</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S75" s="33">
         <v>0.1</v>
@@ -8168,11 +8168,11 @@
       </c>
       <c r="V75" s="31">
         <f t="shared" ref="V75:V83" si="86">V74+(V$84-V$74)/10</f>
-        <v>195.14</v>
-      </c>
-      <c r="W75" s="79">
+        <v>0</v>
+      </c>
+      <c r="W75" s="79" t="e">
         <f t="shared" ref="W75:W84" si="87">V75/$V$74</f>
-        <v>1.0027749229188079</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X75" s="33">
         <v>0.1</v>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AA75" s="31">
         <f t="shared" ref="AA75:AA83" si="88">AA74+(AA$84-AA$74)/10</f>
-        <v>198.45738</v>
+        <v>39.457307999999998</v>
       </c>
       <c r="AB75" s="79">
         <f t="shared" ref="AB75:AB84" si="89">AA75/$AA$74</f>
@@ -8198,11 +8198,11 @@
       </c>
       <c r="AF75" s="31">
         <f t="shared" ref="AF75:AF83" si="90">AF74+(AF$84-AF$74)/10</f>
-        <v>203.56</v>
+        <v>40.574999999999996</v>
       </c>
       <c r="AG75" s="32">
         <f t="shared" si="80"/>
-        <v>1.0007866273352999</v>
+        <v>1.0033382789317506</v>
       </c>
       <c r="AH75" s="33">
         <v>0.1</v>
@@ -8215,11 +8215,11 @@
     <row r="76" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L76" s="31">
         <f t="shared" si="82"/>
-        <v>127.19199999999999</v>
-      </c>
-      <c r="M76" s="79">
+        <v>0</v>
+      </c>
+      <c r="M76" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0055498458376155</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N76" s="33">
         <v>0.2</v>
@@ -8230,11 +8230,11 @@
       </c>
       <c r="Q76" s="31">
         <f t="shared" si="84"/>
-        <v>154.78288000000001</v>
-      </c>
-      <c r="R76" s="79">
+        <v>0</v>
+      </c>
+      <c r="R76" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0055498458376158</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S76" s="33">
         <v>0.2</v>
@@ -8245,11 +8245,11 @@
       </c>
       <c r="V76" s="31">
         <f t="shared" si="86"/>
-        <v>195.67999999999998</v>
-      </c>
-      <c r="W76" s="79">
+        <v>0</v>
+      </c>
+      <c r="W76" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0055498458376155</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X76" s="33">
         <v>0.2</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="AA76" s="31">
         <f t="shared" si="88"/>
-        <v>199.00656000000001</v>
+        <v>39.566496000000001</v>
       </c>
       <c r="AB76" s="79">
         <f t="shared" si="89"/>
@@ -8275,11 +8275,11 @@
       </c>
       <c r="AF76" s="31">
         <f t="shared" si="90"/>
-        <v>203.72</v>
+        <v>40.709999999999994</v>
       </c>
       <c r="AG76" s="32">
         <f t="shared" si="80"/>
-        <v>1.0015732546705998</v>
+        <v>1.0066765578635013</v>
       </c>
       <c r="AH76" s="33">
         <v>0.2</v>
@@ -8292,11 +8292,11 @@
     <row r="77" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L77" s="31">
         <f t="shared" si="82"/>
-        <v>127.54299999999999</v>
-      </c>
-      <c r="M77" s="79">
+        <v>0</v>
+      </c>
+      <c r="M77" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0083247687564234</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N77" s="33">
         <v>0.3</v>
@@ -8307,11 +8307,11 @@
       </c>
       <c r="Q77" s="31">
         <f t="shared" si="84"/>
-        <v>155.21002000000001</v>
-      </c>
-      <c r="R77" s="79">
+        <v>0</v>
+      </c>
+      <c r="R77" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0083247687564236</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S77" s="33">
         <v>0.3</v>
@@ -8322,11 +8322,11 @@
       </c>
       <c r="V77" s="31">
         <f t="shared" si="86"/>
-        <v>196.21999999999997</v>
-      </c>
-      <c r="W77" s="79">
+        <v>0</v>
+      </c>
+      <c r="W77" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0083247687564234</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X77" s="33">
         <v>0.3</v>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="AA77" s="31">
         <f t="shared" si="88"/>
-        <v>199.55574000000001</v>
+        <v>39.675684000000004</v>
       </c>
       <c r="AB77" s="79">
         <f t="shared" si="89"/>
@@ -8352,11 +8352,11 @@
       </c>
       <c r="AF77" s="31">
         <f t="shared" si="90"/>
-        <v>203.88</v>
+        <v>40.844999999999992</v>
       </c>
       <c r="AG77" s="32">
         <f t="shared" si="80"/>
-        <v>1.0023598820058996</v>
+        <v>1.0100148367952522</v>
       </c>
       <c r="AH77" s="33">
         <v>0.3</v>
@@ -8369,11 +8369,11 @@
     <row r="78" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L78" s="31">
         <f t="shared" si="82"/>
-        <v>127.89399999999999</v>
-      </c>
-      <c r="M78" s="79">
+        <v>0</v>
+      </c>
+      <c r="M78" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0110996916752313</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N78" s="33">
         <v>0.4</v>
@@ -8384,11 +8384,11 @@
       </c>
       <c r="Q78" s="31">
         <f t="shared" si="84"/>
-        <v>155.63716000000002</v>
-      </c>
-      <c r="R78" s="79">
+        <v>0</v>
+      </c>
+      <c r="R78" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0110996916752315</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S78" s="33">
         <v>0.4</v>
@@ -8399,11 +8399,11 @@
       </c>
       <c r="V78" s="31">
         <f t="shared" si="86"/>
-        <v>196.75999999999996</v>
-      </c>
-      <c r="W78" s="79">
+        <v>0</v>
+      </c>
+      <c r="W78" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0110996916752311</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X78" s="33">
         <v>0.4</v>
@@ -8414,11 +8414,11 @@
       </c>
       <c r="AA78" s="31">
         <f t="shared" si="88"/>
-        <v>200.10492000000002</v>
+        <v>39.784872000000007</v>
       </c>
       <c r="AB78" s="79">
         <f t="shared" si="89"/>
-        <v>1.0110996916752313</v>
+        <v>1.0110996916752315</v>
       </c>
       <c r="AC78" s="33">
         <v>0.4</v>
@@ -8429,11 +8429,11 @@
       </c>
       <c r="AF78" s="31">
         <f t="shared" si="90"/>
-        <v>204.04</v>
+        <v>40.97999999999999</v>
       </c>
       <c r="AG78" s="32">
         <f t="shared" si="80"/>
-        <v>1.0031465093411995</v>
+        <v>1.0133531157270028</v>
       </c>
       <c r="AH78" s="33">
         <v>0.4</v>
@@ -8446,11 +8446,11 @@
     <row r="79" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L79" s="31">
         <f t="shared" si="82"/>
-        <v>128.245</v>
-      </c>
-      <c r="M79" s="79">
+        <v>0</v>
+      </c>
+      <c r="M79" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0138746145940392</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N79" s="33">
         <v>0.5</v>
@@ -8461,11 +8461,11 @@
       </c>
       <c r="Q79" s="31">
         <f t="shared" si="84"/>
-        <v>156.06430000000003</v>
-      </c>
-      <c r="R79" s="79">
+        <v>0</v>
+      </c>
+      <c r="R79" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0138746145940394</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S79" s="33">
         <v>0.5</v>
@@ -8476,11 +8476,11 @@
       </c>
       <c r="V79" s="31">
         <f t="shared" si="86"/>
-        <v>197.29999999999995</v>
-      </c>
-      <c r="W79" s="79">
+        <v>0</v>
+      </c>
+      <c r="W79" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0138746145940389</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X79" s="33">
         <v>0.5</v>
@@ -8491,11 +8491,11 @@
       </c>
       <c r="AA79" s="31">
         <f t="shared" si="88"/>
-        <v>200.65410000000003</v>
+        <v>39.89406000000001</v>
       </c>
       <c r="AB79" s="79">
         <f t="shared" si="89"/>
-        <v>1.0138746145940392</v>
+        <v>1.0138746145940394</v>
       </c>
       <c r="AC79" s="33">
         <v>0.5</v>
@@ -8506,11 +8506,11 @@
       </c>
       <c r="AF79" s="31">
         <f t="shared" si="90"/>
-        <v>204.2</v>
+        <v>41.114999999999988</v>
       </c>
       <c r="AG79" s="32">
         <f t="shared" si="80"/>
-        <v>1.0039331366764994</v>
+        <v>1.0166913946587535</v>
       </c>
       <c r="AH79" s="33">
         <v>0.5</v>
@@ -8523,11 +8523,11 @@
     <row r="80" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L80" s="31">
         <f t="shared" si="82"/>
-        <v>128.596</v>
-      </c>
-      <c r="M80" s="79">
+        <v>0</v>
+      </c>
+      <c r="M80" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.016649537512847</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N80" s="33">
         <v>0.6</v>
@@ -8538,11 +8538,11 @@
       </c>
       <c r="Q80" s="31">
         <f t="shared" si="84"/>
-        <v>156.49144000000004</v>
-      </c>
-      <c r="R80" s="79">
+        <v>0</v>
+      </c>
+      <c r="R80" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0166495375128473</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S80" s="33">
         <v>0.6</v>
@@ -8553,11 +8553,11 @@
       </c>
       <c r="V80" s="31">
         <f t="shared" si="86"/>
-        <v>197.83999999999995</v>
-      </c>
-      <c r="W80" s="79">
+        <v>0</v>
+      </c>
+      <c r="W80" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0166495375128466</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X80" s="33">
         <v>0.6</v>
@@ -8568,11 +8568,11 @@
       </c>
       <c r="AA80" s="31">
         <f t="shared" si="88"/>
-        <v>201.20328000000003</v>
+        <v>40.003248000000013</v>
       </c>
       <c r="AB80" s="79">
         <f t="shared" si="89"/>
-        <v>1.016649537512847</v>
+        <v>1.0166495375128473</v>
       </c>
       <c r="AC80" s="33">
         <v>0.6</v>
@@ -8583,11 +8583,11 @@
       </c>
       <c r="AF80" s="31">
         <f t="shared" si="90"/>
-        <v>204.35999999999999</v>
+        <v>41.249999999999986</v>
       </c>
       <c r="AG80" s="32">
         <f t="shared" si="80"/>
-        <v>1.0047197640117993</v>
+        <v>1.0200296735905041</v>
       </c>
       <c r="AH80" s="33">
         <v>0.6</v>
@@ -8600,11 +8600,11 @@
     <row r="81" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L81" s="31">
         <f t="shared" si="82"/>
-        <v>128.947</v>
-      </c>
-      <c r="M81" s="79">
+        <v>0</v>
+      </c>
+      <c r="M81" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0194244604316547</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N81" s="33">
         <v>0.7</v>
@@ -8615,11 +8615,11 @@
       </c>
       <c r="Q81" s="31">
         <f t="shared" si="84"/>
-        <v>156.91858000000005</v>
-      </c>
-      <c r="R81" s="79">
+        <v>0</v>
+      </c>
+      <c r="R81" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0194244604316551</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S81" s="33">
         <v>0.7</v>
@@ -8630,11 +8630,11 @@
       </c>
       <c r="V81" s="31">
         <f t="shared" si="86"/>
-        <v>198.37999999999994</v>
-      </c>
-      <c r="W81" s="79">
+        <v>0</v>
+      </c>
+      <c r="W81" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0194244604316545</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X81" s="33">
         <v>0.7</v>
@@ -8645,11 +8645,11 @@
       </c>
       <c r="AA81" s="31">
         <f t="shared" si="88"/>
-        <v>201.75246000000004</v>
+        <v>40.112436000000017</v>
       </c>
       <c r="AB81" s="79">
         <f t="shared" si="89"/>
-        <v>1.0194244604316549</v>
+        <v>1.0194244604316551</v>
       </c>
       <c r="AC81" s="33">
         <v>0.7</v>
@@ -8660,11 +8660,11 @@
       </c>
       <c r="AF81" s="31">
         <f t="shared" si="90"/>
-        <v>204.51999999999998</v>
+        <v>41.384999999999984</v>
       </c>
       <c r="AG81" s="32">
         <f t="shared" si="80"/>
-        <v>1.0055063913470992</v>
+        <v>1.0233679525222548</v>
       </c>
       <c r="AH81" s="33">
         <v>0.7</v>
@@ -8677,11 +8677,11 @@
     <row r="82" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L82" s="31">
         <f t="shared" si="82"/>
-        <v>129.298</v>
-      </c>
-      <c r="M82" s="79">
+        <v>0</v>
+      </c>
+      <c r="M82" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0221993833504626</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N82" s="33">
         <v>0.8</v>
@@ -8692,11 +8692,11 @@
       </c>
       <c r="Q82" s="31">
         <f t="shared" si="84"/>
-        <v>157.34572000000006</v>
-      </c>
-      <c r="R82" s="79">
+        <v>0</v>
+      </c>
+      <c r="R82" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.022199383350463</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S82" s="33">
         <v>0.8</v>
@@ -8707,11 +8707,11 @@
       </c>
       <c r="V82" s="31">
         <f t="shared" si="86"/>
-        <v>198.91999999999993</v>
-      </c>
-      <c r="W82" s="79">
+        <v>0</v>
+      </c>
+      <c r="W82" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0221993833504621</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X82" s="33">
         <v>0.8</v>
@@ -8722,11 +8722,11 @@
       </c>
       <c r="AA82" s="31">
         <f t="shared" si="88"/>
-        <v>202.30164000000005</v>
+        <v>40.22162400000002</v>
       </c>
       <c r="AB82" s="79">
         <f t="shared" si="89"/>
-        <v>1.0221993833504628</v>
+        <v>1.0221993833504632</v>
       </c>
       <c r="AC82" s="33">
         <v>0.8</v>
@@ -8737,11 +8737,11 @@
       </c>
       <c r="AF82" s="31">
         <f t="shared" si="90"/>
-        <v>204.67999999999998</v>
+        <v>41.519999999999982</v>
       </c>
       <c r="AG82" s="32">
         <f t="shared" si="80"/>
-        <v>1.0062930186823991</v>
+        <v>1.0267062314540056</v>
       </c>
       <c r="AH82" s="33">
         <v>0.8</v>
@@ -8754,11 +8754,11 @@
     <row r="83" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L83" s="31">
         <f t="shared" si="82"/>
-        <v>129.649</v>
-      </c>
-      <c r="M83" s="79">
+        <v>0</v>
+      </c>
+      <c r="M83" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0249743062692704</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N83" s="33">
         <v>0.9</v>
@@ -8769,11 +8769,11 @@
       </c>
       <c r="Q83" s="31">
         <f t="shared" si="84"/>
-        <v>157.77286000000007</v>
-      </c>
-      <c r="R83" s="79">
+        <v>0</v>
+      </c>
+      <c r="R83" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0249743062692709</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S83" s="33">
         <v>0.9</v>
@@ -8784,11 +8784,11 @@
       </c>
       <c r="V83" s="31">
         <f t="shared" si="86"/>
-        <v>199.45999999999992</v>
-      </c>
-      <c r="W83" s="79">
+        <v>0</v>
+      </c>
+      <c r="W83" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.02497430626927</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X83" s="33">
         <v>0.9</v>
@@ -8799,11 +8799,11 @@
       </c>
       <c r="AA83" s="31">
         <f t="shared" si="88"/>
-        <v>202.85082000000006</v>
+        <v>40.330812000000023</v>
       </c>
       <c r="AB83" s="79">
         <f t="shared" si="89"/>
-        <v>1.0249743062692707</v>
+        <v>1.0249743062692711</v>
       </c>
       <c r="AC83" s="33">
         <v>0.9</v>
@@ -8814,11 +8814,11 @@
       </c>
       <c r="AF83" s="31">
         <f t="shared" si="90"/>
-        <v>204.83999999999997</v>
+        <v>41.65499999999998</v>
       </c>
       <c r="AG83" s="32">
         <f t="shared" si="80"/>
-        <v>1.0070796460176989</v>
+        <v>1.0300445103857563</v>
       </c>
       <c r="AH83" s="33">
         <v>0.9</v>
@@ -8831,11 +8831,11 @@
     <row r="84" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L84" s="78">
         <f>$AM$8</f>
-        <v>130</v>
-      </c>
-      <c r="M84" s="79">
+        <v>0</v>
+      </c>
+      <c r="M84" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0277492291880781</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N84" s="41">
         <v>1</v>
@@ -8846,11 +8846,11 @@
       </c>
       <c r="Q84" s="78">
         <f>$AN$8</f>
-        <v>158.19999999999999</v>
-      </c>
-      <c r="R84" s="79">
+        <v>0</v>
+      </c>
+      <c r="R84" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0277492291880781</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S84" s="41">
         <v>1</v>
@@ -8861,11 +8861,11 @@
       </c>
       <c r="V84" s="78">
         <f>$AO$8</f>
-        <v>200</v>
-      </c>
-      <c r="W84" s="79">
+        <v>0</v>
+      </c>
+      <c r="W84" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0277492291880781</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X84" s="41">
         <v>1</v>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AA84" s="78">
         <f>$AP$8</f>
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AB84" s="79">
         <f t="shared" si="89"/>
@@ -8891,11 +8891,11 @@
       </c>
       <c r="AF84" s="78">
         <f>$AQ$8</f>
-        <v>205</v>
+        <v>41.79</v>
       </c>
       <c r="AG84" s="81">
         <f t="shared" si="80"/>
-        <v>1.0078662733529991</v>
+        <v>1.0333827893175074</v>
       </c>
       <c r="AH84" s="41">
         <v>1</v>
